--- a/markdown_generator/publications.xlsx
+++ b/markdown_generator/publications.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wchoi/Github Projects/wonchan-choi.github.io/markdown_generator/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wchoi/Github-Repositories/wonchan-choi.github.io/markdown_generator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{601690B7-C446-3142-8895-64BA12BCB8FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E22DA10-143E-BA40-A412-ED5F1A583C2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1360" yWindow="740" windowWidth="28040" windowHeight="16880" xr2:uid="{C1244F33-F08D-274A-A656-7DB80AA6BA4E}"/>
   </bookViews>
@@ -1125,7 +1125,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:8" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>43892</v>
       </c>
@@ -1151,16 +1151,6 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:8" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="8" spans="1:8" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="9" spans="1:8" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="10" spans="1:8" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="11" spans="1:8" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="12" spans="1:8" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="13" spans="1:8" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="14" spans="1:8" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="15" spans="1:8" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="16" spans="1:8" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="17" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="18" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="19" customFormat="1" x14ac:dyDescent="0.2"/>

--- a/markdown_generator/publications.xlsx
+++ b/markdown_generator/publications.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wchoi/Github-Repositories/wonchan-choi.github.io/markdown_generator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E22DA10-143E-BA40-A412-ED5F1A583C2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90C8F54C-E92E-D148-8839-183EC7E81792}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1360" yWindow="740" windowWidth="28040" windowHeight="16880" xr2:uid="{C1244F33-F08D-274A-A656-7DB80AA6BA4E}"/>
+    <workbookView xWindow="1360" yWindow="740" windowWidth="34400" windowHeight="20900" xr2:uid="{C1244F33-F08D-274A-A656-7DB80AA6BA4E}"/>
   </bookViews>
   <sheets>
     <sheet name="publications" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="77">
   <si>
     <t>pub_date</t>
   </si>
@@ -46,83 +46,877 @@
     <t>slides_url</t>
   </si>
   <si>
-    <t>Journal 1</t>
-  </si>
-  <si>
-    <t>This paper is about the number 1. The number 2 is left for future work.</t>
-  </si>
-  <si>
-    <t>Your Name, You. (2009). "Paper Title Number 1." &lt;i&gt;Journal 1&lt;/i&gt;. 1(1).</t>
-  </si>
-  <si>
-    <t>paper-title-number-1</t>
-  </si>
-  <si>
-    <t>http://academicpages.github.io/files/paper1.pdf</t>
-  </si>
-  <si>
-    <t>http://academicpages.github.io/files/slides1.pdf</t>
-  </si>
-  <si>
-    <t>This paper is about the number 2. The number 3 is left for future work.</t>
-  </si>
-  <si>
-    <t>Your Name, You. (2010). "Paper Title Number 2." &lt;i&gt;Journal 1&lt;/i&gt;. 1(2).</t>
-  </si>
-  <si>
-    <t>paper-title-number-2</t>
-  </si>
-  <si>
-    <t>http://academicpages.github.io/files/paper2.pdf</t>
-  </si>
-  <si>
-    <t>http://academicpages.github.io/files/slides2.pdf</t>
-  </si>
-  <si>
-    <t>This paper is about the number 3. The number 4 is left for future work.</t>
-  </si>
-  <si>
-    <t>Choi, W</t>
-  </si>
-  <si>
-    <t>paper-title-number-3</t>
-  </si>
-  <si>
-    <t>http://academicpages.github.io/files/paper3.pdf</t>
-  </si>
-  <si>
-    <t>http://academicpages.github.io/files/slides3.pdf</t>
-  </si>
-  <si>
-    <t>a</t>
-  </si>
-  <si>
-    <t>b</t>
-  </si>
-  <si>
-    <t>c</t>
-  </si>
-  <si>
-    <t>d</t>
-  </si>
-  <si>
-    <t>Journal 2</t>
-  </si>
-  <si>
-    <t>Journal 3</t>
-  </si>
-  <si>
-    <t>Journal 4</t>
-  </si>
-  <si>
-    <t>y</t>
+    <r>
+      <t xml:space="preserve">Zheng, Z., Oh, H., Mim, M., </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Choi, W.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, &amp; Lee, Y. (2023). An exploration of robot-mediated Tai Chi exercise for older adults. </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Applied Sciences, 13</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>(9), 5306. https://doi.org/10.3390/app13095306 [Refereed]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Choi, W.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, Stvilia, B. &amp; Lee, H. S. (2023). Developing a platform-specific framework for web credibility assessment: A case of social Q&amp;A sites. </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Information Processing and Management, 60</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>(3), 103321. https://doi.org/10.1016/j.ipm.2023.103321 [Refereed]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Choi, W.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, Kim, S.Y., &amp; Luo, M. (2022). Design matters in web credibility assessment: Interactive design as a social validation tool for online health information seekers. </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Asian Communication Research, 19</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>(3), 119–138. https://doi.org/10.20879/acr.2022.19.3.119 [Refereed]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Park, M., Lee, Y., &amp; </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Choi, W.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> (2022). Understanding the research landscape of information and communication technology integration in dementia-focused assistive technologies: Mining literature from 1970 to 2020. </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Gerontechnology, 21</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>(1), 1–18. https://doi.org/10.4017/gt.2022.21.1.798.12 [Refereed]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Lee, Y., </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Choi, W.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, &amp; Park, M. (2022). Respite service use among dementia and nondementia caregivers: Findings from the National Caregiving in the U.S. 2015 Survey. </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Journal of Applied Gerontology, 41</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>(6), 1557–1567. https://doi.org/10.1177/07334648221075620 [Refereed]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Choi, W.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, Park, M. S., &amp; Lee, Y. (2022). Associations between mastery of life and everyday life information-seeking behavior among older adults: Analysis of the Pew Research Center’s information engaged and information wary survey data. </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Journal of the Association for Information Science &amp; Technology, 73</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>(3), 393–406. https://doi.org/10.1002/asi.24556 [Refereed]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Wang, S., Lee, H. S., &amp; </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Choi, W.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> (2021). A feature-oriented analysis of developers’ descriptions and user reviews of top mHealth applications for diabetes and hypertension. </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>International Journal of Medical Informatics, 156</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>, 104598.</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>https://doi.org/10.1016/j.ijmedinf.2021.104598 [Refereed]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Choi, W.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, Wang, S., Lee, Y., Oh, H., &amp; Zheng, Z. (2020). A systematic review of mobile health technologies to support self-management of concurrent diabetes and hypertension. </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Journal of the American Medical Informatics Association, 27</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>(6), 939–945. https://doi.org/doi:10.1093/jamia/ocaa029 [Refereed]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Choi, W.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> (2020). Older adults’ credibility assessment of online health information: An exploratory study using an extended typology of web credibility. </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Journal of the Association for Information Science and Technology, 71</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>(11), 1295–1307. https://doi.org/doi:10.1002/asi.24341 [Refereed]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Choi, W.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> (2019). Older adults’ health information behavior in everyday life settings. </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Library &amp; Information Science Research, 41</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>(4), 100983. https://doi.org/doi:10.1016/j.lisr.2019.100983 [Refereed]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Choi, W.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, Zheng, H., Franklin, P. &amp; Tulu, B. (2019). mHealth technologies for osteoarthritis self-management and treatment: A systematic review. </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Health Informatics Journal, 25</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>(3), 984–1003. https://doi.org/doi:10.1177/1460458217735676 [Refereed]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Zheng, H., Tulu, B., </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Choi, W.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>, &amp; Franklin, P. (2017). Using mHealth app to support treatment decision making for knee arthritis: Patient perspective.</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> eGEMs, 5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>(2). https://doi.org/doi:10.13063/2327-9214.1284 [Refereed]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Yang, K., Lee, J., &amp; </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Choi, W.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> (2016). Publication and citation patterns of Korean LIS research by subject areas. </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Malaysian Journal of Library &amp; Information Science, 21</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>(2), 67–81. https://doi.org/doi:10.22452/mjlis.vol21no2.5 [Refereed]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Yang, K., Lee, J., &amp; </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Choi, W.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> (2015). Looking beyond the numbers: Bibliometric approach to analysis of LIS research in Korea. </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Journal of the Korean Society for Library and Information Science, 49</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>(4), 241–264. https://doi.org/doi:10.4275/KSLIS.2015.49.4.241 [Refereed]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Stvilia, B., &amp; </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Choi, W.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> (2015). Mobile wellness application-seeking behavior by college students: An exploratory study. </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Library &amp; Information Science Research, 37</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>(3), 201–208. https://doi.org/doi:10.1016/j.lisr.2015.04.007 [Refereed]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Choi, W.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, &amp; Stvilia, B. (2015). Web credibility assessment: Conceptualization, operationalization, variability, and models. </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Journal of the Association for Information Science and Technology, 66</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>(12), 2399–ßßß2414. https://doi.org/doi:10.1002/asi.23543 [Refereed]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Chang, D. H., &amp; </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Choi, W.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> (2008). Developing and testing of an e-journal evaluation model for university libraries. </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Journal of the Korean Society for Information Management, 25</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>(4), 165–184. https://doi.org/doi:10.3743/KOSIM.2008.25.4.165 [Refereed]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Chang, D. H., &amp; </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Choi, W.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> (2008). Trends in integrated electronic resource management in academic libraries. </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Journal of the Korean Society for Library and Information Science, 42</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>(4), 201–221. https://doi.org/doi:10.4275/KSLIS.2008.42.4.201 [Refereed]</t>
+    </r>
+  </si>
+  <si>
+    <t>An exploration of robot-mediated Tai Chi exercise for older adults</t>
+  </si>
+  <si>
+    <t>Applied Sciences</t>
+  </si>
+  <si>
+    <t>Developing a platform-specific framework for web credibility assessment: A case of social Q&amp;A sites</t>
+  </si>
+  <si>
+    <t>Information Processing and Management</t>
+  </si>
+  <si>
+    <t>Design matters in web credibility assessment: Interactive design as a social validation tool for online health information seekers</t>
+  </si>
+  <si>
+    <t>Asian Communication Research</t>
+  </si>
+  <si>
+    <t>Understanding the research landscape of information and communication technology integration in dementia-focused assistive technologies: Mining literature from 1970 to 2020</t>
+  </si>
+  <si>
+    <t>Gerontechnology</t>
+  </si>
+  <si>
+    <t>Respite service use among dementia and nondementia caregivers: Findings from the National Caregiving in the U.S. 2015 Survey</t>
+  </si>
+  <si>
+    <t>Journal of Applied Gerontology</t>
+  </si>
+  <si>
+    <t>Associations between mastery of life and everyday life information-seeking behavior among older adults: Analysis of the Pew Research Center’s information engaged and information wary survey data</t>
+  </si>
+  <si>
+    <t>Journal of the Association for Information Science &amp; Technology</t>
+  </si>
+  <si>
+    <t>A feature-oriented analysis of developers’ descriptions and user reviews of top mHealth applications for diabetes and hypertension</t>
+  </si>
+  <si>
+    <t>International Journal of Medical Informatics</t>
+  </si>
+  <si>
+    <t>A systematic review of mobile health technologies to support self-management of concurrent diabetes and hypertension</t>
+  </si>
+  <si>
+    <t>Journal of the American Medical Informatics Association</t>
+  </si>
+  <si>
+    <t>Older adults’ credibility assessment of online health information: An exploratory study using an extended typology of web credibility</t>
+  </si>
+  <si>
+    <t>Journal of the Association for Information Science and Technology</t>
+  </si>
+  <si>
+    <t>Older adults’ health information behavior in everyday life settings</t>
+  </si>
+  <si>
+    <t>Library &amp; Information Science Research</t>
+  </si>
+  <si>
+    <t>mHealth technologies for osteoarthritis self-management and treatment: A systematic review</t>
+  </si>
+  <si>
+    <t>Health Informatics Journal</t>
+  </si>
+  <si>
+    <t>Using mHealth app to support treatment decision making for knee arthritis: Patient perspective</t>
+  </si>
+  <si>
+    <t>eGEMs</t>
+  </si>
+  <si>
+    <t>Publication and citation patterns of Korean LIS research by subject areas</t>
+  </si>
+  <si>
+    <t>Malaysian Journal of Library &amp; Information Science</t>
+  </si>
+  <si>
+    <t>Looking beyond the numbers: Bibliometric approach to analysis of LIS research in Korea</t>
+  </si>
+  <si>
+    <t>Journal of the Korean Society for Library and Information Science</t>
+  </si>
+  <si>
+    <t>Mobile wellness application-seeking behavior by college students: An exploratory study</t>
+  </si>
+  <si>
+    <t>Web credibility assessment: Conceptualization, operationalization, variability, and models</t>
+  </si>
+  <si>
+    <t>Developing and testing of an e-journal evaluation model for university libraries</t>
+  </si>
+  <si>
+    <t>Journal of the Korean Society for Information Management</t>
+  </si>
+  <si>
+    <t>Trends in integrated electronic resource management in academic libraries</t>
+  </si>
+  <si>
+    <t>2023-AS</t>
+  </si>
+  <si>
+    <t>2023-IPM</t>
+  </si>
+  <si>
+    <t>2022-ACR</t>
+  </si>
+  <si>
+    <t>2022-Geron</t>
+  </si>
+  <si>
+    <t>2022-JAG</t>
+  </si>
+  <si>
+    <t>2022-JASIST</t>
+  </si>
+  <si>
+    <t>2021-IJMI</t>
+  </si>
+  <si>
+    <t>2020-JAMIA</t>
+  </si>
+  <si>
+    <t>2020-JASIST</t>
+  </si>
+  <si>
+    <t>2019-LISR</t>
+  </si>
+  <si>
+    <t>2019-HIJ</t>
+  </si>
+  <si>
+    <t>2017-eGEMs</t>
+  </si>
+  <si>
+    <t>2015-MJLIS</t>
+  </si>
+  <si>
+    <t>2015-JKSLIS</t>
+  </si>
+  <si>
+    <t>2015-LISR</t>
+  </si>
+  <si>
+    <t>2015-JASIST</t>
+  </si>
+  <si>
+    <t>2008-JKSIM</t>
+  </si>
+  <si>
+    <t>2008-JKSLIS</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -262,6 +1056,26 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="33">
@@ -605,9 +1419,20 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -983,183 +1808,350 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AA85793-BCD8-2741-A85B-C8AEED21BC9A}">
-  <dimension ref="A1:H25"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:H19"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="74.5" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="56.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="58.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="40.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.33203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="74.5" style="1"/>
+    <col min="3" max="3" width="21.1640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="37.5" style="1" customWidth="1"/>
+    <col min="5" max="5" width="74.5" style="1"/>
+    <col min="6" max="6" width="27.33203125" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="74.5" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+    <row r="1" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A2" s="1">
-        <v>29515</v>
-      </c>
-      <c r="B2" t="s">
+    <row r="2" spans="1:8" ht="51" x14ac:dyDescent="0.2">
+      <c r="A2" s="4">
+        <v>45287</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="51" x14ac:dyDescent="0.2">
+      <c r="A3" s="4">
+        <v>45288</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="68" x14ac:dyDescent="0.2">
+      <c r="A4" s="4">
+        <v>44924</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="68" x14ac:dyDescent="0.2">
+      <c r="A5" s="4">
+        <v>44925</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="68" x14ac:dyDescent="0.2">
+      <c r="A6" s="4">
+        <v>44926</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="85" x14ac:dyDescent="0.2">
+      <c r="A7" s="4">
+        <v>44562</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="68" x14ac:dyDescent="0.2">
+      <c r="A8" s="4">
+        <v>44198</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="68" x14ac:dyDescent="0.2">
+      <c r="A9" s="4">
+        <v>43833</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="68" x14ac:dyDescent="0.2">
+      <c r="A10" s="4">
+        <v>43469</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="51" x14ac:dyDescent="0.2">
+      <c r="A11" s="4">
+        <v>43470</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="51" x14ac:dyDescent="0.2">
+      <c r="A12" s="4">
+        <v>43471</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="51" x14ac:dyDescent="0.2">
+      <c r="A13" s="4">
+        <v>42742</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="51" x14ac:dyDescent="0.2">
+      <c r="A14" s="4">
+        <v>42012</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="68" x14ac:dyDescent="0.2">
+      <c r="A15" s="4">
+        <v>42013</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="51" x14ac:dyDescent="0.2">
+      <c r="A16" s="4">
+        <v>42014</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="68" x14ac:dyDescent="0.2">
+      <c r="A17" s="4">
+        <v>42015</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="68" x14ac:dyDescent="0.2">
+      <c r="A18" s="4">
+        <v>39459</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H2" t="s">
-        <v>13</v>
+      <c r="F18" s="1" t="s">
+        <v>75</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A3" s="1">
-        <v>30258</v>
-      </c>
-      <c r="B3" t="s">
+    <row r="19" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+      <c r="A19" s="4">
+        <v>39460</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" t="s">
-        <v>15</v>
-      </c>
-      <c r="F3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H3" t="s">
-        <v>18</v>
+      <c r="F19" s="1" t="s">
+        <v>76</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A4" s="1">
-        <v>42874</v>
-      </c>
-      <c r="B4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E4" t="s">
-        <v>20</v>
-      </c>
-      <c r="F4" t="s">
-        <v>21</v>
-      </c>
-      <c r="G4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A5" s="1">
-        <v>43892</v>
-      </c>
-      <c r="B5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E5" t="s">
-        <v>20</v>
-      </c>
-      <c r="F5" t="s">
-        <v>21</v>
-      </c>
-      <c r="G5" t="s">
-        <v>22</v>
-      </c>
-      <c r="H5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A6" s="1">
-        <v>43892</v>
-      </c>
-      <c r="B6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C6" t="s">
-        <v>30</v>
-      </c>
-      <c r="D6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E6" t="s">
-        <v>20</v>
-      </c>
-      <c r="F6" t="s">
-        <v>21</v>
-      </c>
-      <c r="G6" t="s">
-        <v>22</v>
-      </c>
-      <c r="H6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="17" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="18" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="19" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="20" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="21" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="22" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="23" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="24" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="25" customFormat="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/markdown_generator/publications.xlsx
+++ b/markdown_generator/publications.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wchoi/Github-Repositories/wonchan-choi.github.io/markdown_generator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90C8F54C-E92E-D148-8839-183EC7E81792}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FF0F2F3-FFCC-244B-968B-37D9F6C34A21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1360" yWindow="740" windowWidth="34400" windowHeight="20900" xr2:uid="{C1244F33-F08D-274A-A656-7DB80AA6BA4E}"/>
+    <workbookView xWindow="-51200" yWindow="500" windowWidth="51200" windowHeight="28300" xr2:uid="{C1244F33-F08D-274A-A656-7DB80AA6BA4E}"/>
   </bookViews>
   <sheets>
     <sheet name="publications" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="74">
   <si>
     <t>pub_date</t>
   </si>
@@ -858,65 +858,56 @@
     <t>Trends in integrated electronic resource management in academic libraries</t>
   </si>
   <si>
-    <t>2023-AS</t>
-  </si>
-  <si>
-    <t>2023-IPM</t>
-  </si>
-  <si>
-    <t>2022-ACR</t>
-  </si>
-  <si>
-    <t>2022-Geron</t>
-  </si>
-  <si>
-    <t>2022-JAG</t>
-  </si>
-  <si>
-    <t>2022-JASIST</t>
-  </si>
-  <si>
-    <t>2021-IJMI</t>
-  </si>
-  <si>
-    <t>2020-JAMIA</t>
-  </si>
-  <si>
-    <t>2020-JASIST</t>
-  </si>
-  <si>
-    <t>2019-LISR</t>
-  </si>
-  <si>
-    <t>2019-HIJ</t>
-  </si>
-  <si>
-    <t>2017-eGEMs</t>
-  </si>
-  <si>
-    <t>2015-MJLIS</t>
-  </si>
-  <si>
-    <t>2015-JKSLIS</t>
-  </si>
-  <si>
-    <t>2015-LISR</t>
-  </si>
-  <si>
-    <t>2015-JASIST</t>
-  </si>
-  <si>
-    <t>2008-JKSIM</t>
-  </si>
-  <si>
-    <t>2008-JKSLIS</t>
+    <t>https://www.mdpi.com/2076-3417/13/9/5306</t>
+  </si>
+  <si>
+    <t>In this fast-aging society, many older adults fail to meet the required level of exercise due to trainer shortages. Therefore, we developed a robot tutor to investigate the feasibility of robot-mediated exercise for older adults. Twenty older adults participated in an experimental study. A pre-exercise survey was used to assess their background. Each participant experienced a 30-min robot-led Tai Chi exercise followed by a post-exercise survey to evaluate the easiness of following the robot and expectations for future robot design. Participants’ Tai Chi performances were evaluated in terms of completion and accuracy. Associations between the surveys and the performance were also analyzed. All participants completed the study. Fifteen out of the twenty subjects had at least one chronic condition, and most practiced Tai Chi before the study but had never interacted with a robot. On average, the participants scored 93.09 and 85.21 out of 100 for movement completion and accuracy, respectively. Their initial movement accuracy was correlated with their attitude towards exercise. Most subjects reported that they could follow the robot’s movements and speeches well and were interested in using a robot tutor in the community. The study demonstrated the initial feasibility of robot-led Tai Chi exercise for older adults.</t>
+  </si>
+  <si>
+    <t>AS</t>
+  </si>
+  <si>
+    <t>IPM</t>
+  </si>
+  <si>
+    <t>ACR</t>
+  </si>
+  <si>
+    <t>Geron</t>
+  </si>
+  <si>
+    <t>JAG</t>
+  </si>
+  <si>
+    <t>JASIST</t>
+  </si>
+  <si>
+    <t>IJMI</t>
+  </si>
+  <si>
+    <t>JAMIA</t>
+  </si>
+  <si>
+    <t>LISR</t>
+  </si>
+  <si>
+    <t>HIJ</t>
+  </si>
+  <si>
+    <t>MJLIS</t>
+  </si>
+  <si>
+    <t>JKSLIS</t>
+  </si>
+  <si>
+    <t>JKSIM</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1076,6 +1067,14 @@
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
@@ -1375,7 +1374,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="42">
+  <cellStyleXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
@@ -1418,23 +1417,27 @@
     <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="42" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="42">
+  <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
     <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
     <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
@@ -1468,6 +1471,7 @@
     <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
     <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
     <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Hyperlink" xfId="42" builtinId="8"/>
     <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
     <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
     <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
@@ -1811,349 +1815,358 @@
   <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="74.5" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="20.33203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="74.5" style="1"/>
-    <col min="3" max="3" width="21.1640625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="37.5" style="1" customWidth="1"/>
-    <col min="5" max="5" width="74.5" style="1"/>
-    <col min="6" max="6" width="27.33203125" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="74.5" style="1"/>
+    <col min="1" max="1" width="20.33203125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="74.5" style="2"/>
+    <col min="3" max="3" width="21.1640625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="68.6640625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="74.5" style="2"/>
+    <col min="6" max="6" width="27.33203125" style="2" customWidth="1"/>
+    <col min="7" max="16384" width="74.5" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="17" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="51" x14ac:dyDescent="0.2">
-      <c r="A2" s="4">
+    <row r="2" spans="1:8" ht="289" x14ac:dyDescent="0.2">
+      <c r="A2" s="3">
         <v>45287</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="D2" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="51" x14ac:dyDescent="0.2">
-      <c r="A3" s="4">
+      <c r="A3" s="3">
         <v>45288</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>60</v>
+      <c r="F3" s="2" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="68" x14ac:dyDescent="0.2">
-      <c r="A4" s="4">
+      <c r="A4" s="3">
         <v>44924</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="1" t="s">
-        <v>61</v>
+      <c r="F4" s="2" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="68" x14ac:dyDescent="0.2">
-      <c r="A5" s="4">
+      <c r="A5" s="3">
         <v>44925</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F5" s="1" t="s">
-        <v>62</v>
+      <c r="F5" s="2" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="68" x14ac:dyDescent="0.2">
-      <c r="A6" s="4">
+      <c r="A6" s="3">
         <v>44926</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F6" s="1" t="s">
-        <v>63</v>
+      <c r="F6" s="2" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="85" x14ac:dyDescent="0.2">
-      <c r="A7" s="4">
+      <c r="A7" s="3">
         <v>44562</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E7" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F7" s="1" t="s">
-        <v>64</v>
+      <c r="F7" s="2" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="68" x14ac:dyDescent="0.2">
-      <c r="A8" s="4">
+      <c r="A8" s="3">
         <v>44198</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E8" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="F8" s="1" t="s">
-        <v>65</v>
+      <c r="F8" s="2" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="68" x14ac:dyDescent="0.2">
-      <c r="A9" s="4">
+      <c r="A9" s="3">
         <v>43833</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="E9" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="F9" s="1" t="s">
-        <v>66</v>
+      <c r="F9" s="2" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="68" x14ac:dyDescent="0.2">
-      <c r="A10" s="4">
+      <c r="A10" s="3">
         <v>43469</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="E10" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="F10" s="1" t="s">
-        <v>67</v>
+      <c r="F10" s="2" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="51" x14ac:dyDescent="0.2">
-      <c r="A11" s="4">
+      <c r="A11" s="3">
         <v>43470</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="E11" s="3" t="s">
+      <c r="E11" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="F11" s="1" t="s">
-        <v>68</v>
+      <c r="F11" s="2" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="51" x14ac:dyDescent="0.2">
-      <c r="A12" s="4">
+      <c r="A12" s="3">
         <v>43471</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C12" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="E12" s="3" t="s">
+      <c r="E12" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="F12" s="1" t="s">
-        <v>69</v>
+      <c r="F12" s="2" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="51" x14ac:dyDescent="0.2">
-      <c r="A13" s="4">
+      <c r="A13" s="3">
         <v>42742</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B13" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C13" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="E13" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F13" s="1" t="s">
-        <v>70</v>
+      <c r="F13" s="2" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="51" x14ac:dyDescent="0.2">
-      <c r="A14" s="4">
+      <c r="A14" s="3">
         <v>42012</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C14" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="E14" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="F14" s="1" t="s">
+      <c r="F14" s="2" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="68" x14ac:dyDescent="0.2">
-      <c r="A15" s="4">
+      <c r="A15" s="3">
         <v>42013</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B15" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="C15" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="E15" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="F15" s="1" t="s">
+      <c r="F15" s="2" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="51" x14ac:dyDescent="0.2">
-      <c r="A16" s="4">
+      <c r="A16" s="3">
         <v>42014</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B16" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="C16" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="E16" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="F16" s="1" t="s">
-        <v>73</v>
+      <c r="F16" s="2" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="68" x14ac:dyDescent="0.2">
-      <c r="A17" s="4">
+      <c r="A17" s="3">
         <v>42015</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B17" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="C17" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E17" s="3" t="s">
+      <c r="E17" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="F17" s="1" t="s">
-        <v>74</v>
+      <c r="F17" s="2" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="68" x14ac:dyDescent="0.2">
-      <c r="A18" s="4">
+      <c r="A18" s="3">
         <v>39459</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="B18" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="C18" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E18" s="2" t="s">
+      <c r="E18" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="F18" s="1" t="s">
-        <v>75</v>
+      <c r="F18" s="2" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A19" s="4">
+      <c r="A19" s="3">
         <v>39460</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="B19" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="C19" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E19" s="2" t="s">
+      <c r="E19" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="F19" s="1" t="s">
-        <v>76</v>
+      <c r="F19" s="2" t="s">
+        <v>72</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="G2" r:id="rId1" xr:uid="{35C9EA02-369B-E84D-9225-C6DD2AC49F17}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/markdown_generator/publications.xlsx
+++ b/markdown_generator/publications.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wchoi/Github-Repositories/wonchan-choi.github.io/markdown_generator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FF0F2F3-FFCC-244B-968B-37D9F6C34A21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FFD11DF-D2F2-914B-8DE9-6F412649B0D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-51200" yWindow="500" windowWidth="51200" windowHeight="28300" xr2:uid="{C1244F33-F08D-274A-A656-7DB80AA6BA4E}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="76">
   <si>
     <t>pub_date</t>
   </si>
@@ -901,6 +901,12 @@
   </si>
   <si>
     <t>JKSIM</t>
+  </si>
+  <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>journal</t>
   </si>
 </sst>
 </file>
@@ -1812,360 +1818,417 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AA85793-BCD8-2741-A85B-C8AEED21BC9A}">
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="74.5" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="20.33203125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="74.5" style="2"/>
-    <col min="3" max="3" width="21.1640625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="68.6640625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="74.5" style="2"/>
-    <col min="6" max="6" width="27.33203125" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="74.5" style="2"/>
+    <col min="1" max="2" width="20.33203125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="74.5" style="2"/>
+    <col min="4" max="4" width="21.1640625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="68.6640625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="74.5" style="2"/>
+    <col min="7" max="7" width="27.33203125" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="74.5" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" ht="17" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="289" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" ht="289" x14ac:dyDescent="0.2">
       <c r="A2" s="3">
         <v>45287</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="F2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="51" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9" ht="51" x14ac:dyDescent="0.2">
       <c r="A3" s="3">
         <v>45288</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="F3" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="G3" s="2" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="68" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9" ht="68" x14ac:dyDescent="0.2">
       <c r="A4" s="3">
         <v>44924</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="F4" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="G4" s="2" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="68" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9" ht="68" x14ac:dyDescent="0.2">
       <c r="A5" s="3">
         <v>44925</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="F5" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="G5" s="2" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="68" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:9" ht="68" x14ac:dyDescent="0.2">
       <c r="A6" s="3">
         <v>44926</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="F6" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="G6" s="2" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="85" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:9" ht="85" x14ac:dyDescent="0.2">
       <c r="A7" s="3">
         <v>44562</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="F7" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="G7" s="2" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="68" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:9" ht="68" x14ac:dyDescent="0.2">
       <c r="A8" s="3">
         <v>44198</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="D8" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="F8" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="G8" s="2" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="68" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:9" ht="68" x14ac:dyDescent="0.2">
       <c r="A9" s="3">
         <v>43833</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="D9" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="F9" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="G9" s="2" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="68" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:9" ht="68" x14ac:dyDescent="0.2">
       <c r="A10" s="3">
         <v>43469</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="D10" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="F10" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="G10" s="2" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="51" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:9" ht="51" x14ac:dyDescent="0.2">
       <c r="A11" s="3">
         <v>43470</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="D11" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="F11" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="G11" s="2" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="51" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:9" ht="51" x14ac:dyDescent="0.2">
       <c r="A12" s="3">
         <v>43471</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="D12" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="F12" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="F12" s="2" t="s">
+      <c r="G12" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="51" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:9" ht="51" x14ac:dyDescent="0.2">
       <c r="A13" s="3">
         <v>42742</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="D13" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="F13" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F13" s="2" t="s">
+      <c r="G13" s="2" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="51" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:9" ht="51" x14ac:dyDescent="0.2">
       <c r="A14" s="3">
         <v>42012</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="D14" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="F14" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="F14" s="2" t="s">
+      <c r="G14" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="68" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:9" ht="68" x14ac:dyDescent="0.2">
       <c r="A15" s="3">
         <v>42013</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="D15" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="F15" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="F15" s="2" t="s">
+      <c r="G15" s="2" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="51" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:9" ht="51" x14ac:dyDescent="0.2">
       <c r="A16" s="3">
         <v>42014</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="D16" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="F16" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="F16" s="2" t="s">
+      <c r="G16" s="2" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="68" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7" ht="68" x14ac:dyDescent="0.2">
       <c r="A17" s="3">
         <v>42015</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B17" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="D17" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E17" s="5" t="s">
+      <c r="F17" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="F17" s="2" t="s">
+      <c r="G17" s="2" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="68" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7" ht="68" x14ac:dyDescent="0.2">
       <c r="A18" s="3">
         <v>39459</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B18" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="D18" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E18" s="4" t="s">
+      <c r="F18" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="F18" s="2" t="s">
+      <c r="G18" s="2" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7" ht="51" x14ac:dyDescent="0.2">
       <c r="A19" s="3">
         <v>39460</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B19" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="D19" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E19" s="4" t="s">
+      <c r="F19" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="F19" s="2" t="s">
+      <c r="G19" s="2" t="s">
         <v>72</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="G2" r:id="rId1" xr:uid="{35C9EA02-369B-E84D-9225-C6DD2AC49F17}"/>
+    <hyperlink ref="H2" r:id="rId1" xr:uid="{35C9EA02-369B-E84D-9225-C6DD2AC49F17}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/markdown_generator/publications.xlsx
+++ b/markdown_generator/publications.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wchoi/Github-Repositories/wonchan-choi.github.io/markdown_generator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FFD11DF-D2F2-914B-8DE9-6F412649B0D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{231E6709-548A-C246-8055-8884CCFA22A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-51200" yWindow="500" windowWidth="51200" windowHeight="28300" xr2:uid="{C1244F33-F08D-274A-A656-7DB80AA6BA4E}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="77">
   <si>
     <t>pub_date</t>
   </si>
@@ -907,6 +907,9 @@
   </si>
   <si>
     <t>journal</t>
+  </si>
+  <si>
+    <t>Journal Articles</t>
   </si>
 </sst>
 </file>
@@ -1890,7 +1893,7 @@
         <v>45288</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>28</v>
@@ -1910,7 +1913,7 @@
         <v>44924</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>30</v>
@@ -1930,7 +1933,7 @@
         <v>44925</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>32</v>
@@ -1950,7 +1953,7 @@
         <v>44926</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>34</v>
@@ -1970,7 +1973,7 @@
         <v>44562</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>36</v>
@@ -1990,7 +1993,7 @@
         <v>44198</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>38</v>
@@ -2010,7 +2013,7 @@
         <v>43833</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>40</v>
@@ -2030,7 +2033,7 @@
         <v>43469</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>42</v>
@@ -2050,7 +2053,7 @@
         <v>43470</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>44</v>
@@ -2070,7 +2073,7 @@
         <v>43471</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>46</v>
@@ -2090,7 +2093,7 @@
         <v>42742</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>48</v>
@@ -2110,7 +2113,7 @@
         <v>42012</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>50</v>
@@ -2130,7 +2133,7 @@
         <v>42013</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>52</v>
@@ -2150,7 +2153,7 @@
         <v>42014</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>54</v>
@@ -2170,7 +2173,7 @@
         <v>42015</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>55</v>
@@ -2190,7 +2193,7 @@
         <v>39459</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>56</v>
@@ -2210,7 +2213,7 @@
         <v>39460</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>58</v>

--- a/markdown_generator/publications.xlsx
+++ b/markdown_generator/publications.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wchoi/Github-Repositories/wonchan-choi.github.io/markdown_generator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{231E6709-548A-C246-8055-8884CCFA22A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0A2265F-EB92-FA40-8C65-A423DA9FEFFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-51200" yWindow="500" windowWidth="51200" windowHeight="28300" xr2:uid="{C1244F33-F08D-274A-A656-7DB80AA6BA4E}"/>
   </bookViews>

--- a/markdown_generator/publications.xlsx
+++ b/markdown_generator/publications.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wchoi/Github-Repositories/wonchan-choi.github.io/markdown_generator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0A2265F-EB92-FA40-8C65-A423DA9FEFFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83D9FBF4-91A9-1344-9162-65031911AFA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-51200" yWindow="500" windowWidth="51200" windowHeight="28300" xr2:uid="{C1244F33-F08D-274A-A656-7DB80AA6BA4E}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="76">
   <si>
     <t>pub_date</t>
   </si>
@@ -904,9 +904,6 @@
   </si>
   <si>
     <t>type</t>
-  </si>
-  <si>
-    <t>journal</t>
   </si>
   <si>
     <t>Journal Articles</t>
@@ -1893,7 +1890,7 @@
         <v>45288</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>28</v>
@@ -1913,7 +1910,7 @@
         <v>44924</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>30</v>
@@ -1933,7 +1930,7 @@
         <v>44925</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>32</v>
@@ -1953,7 +1950,7 @@
         <v>44926</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>34</v>
@@ -1973,7 +1970,7 @@
         <v>44562</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>36</v>
@@ -1993,7 +1990,7 @@
         <v>44198</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>38</v>
@@ -2013,7 +2010,7 @@
         <v>43833</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>40</v>
@@ -2033,7 +2030,7 @@
         <v>43469</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>42</v>
@@ -2053,7 +2050,7 @@
         <v>43470</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>44</v>
@@ -2073,7 +2070,7 @@
         <v>43471</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>46</v>
@@ -2093,7 +2090,7 @@
         <v>42742</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>48</v>
@@ -2113,7 +2110,7 @@
         <v>42012</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>50</v>
@@ -2133,7 +2130,7 @@
         <v>42013</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>52</v>
@@ -2153,7 +2150,7 @@
         <v>42014</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>54</v>
@@ -2173,7 +2170,7 @@
         <v>42015</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>55</v>
@@ -2193,7 +2190,7 @@
         <v>39459</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>56</v>
@@ -2213,7 +2210,7 @@
         <v>39460</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>58</v>

--- a/markdown_generator/publications.xlsx
+++ b/markdown_generator/publications.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wchoi/Github-Repositories/wonchan-choi.github.io/markdown_generator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83D9FBF4-91A9-1344-9162-65031911AFA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B3091AA-B165-664A-A897-1C8F2D842869}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-51200" yWindow="500" windowWidth="51200" windowHeight="28300" xr2:uid="{C1244F33-F08D-274A-A656-7DB80AA6BA4E}"/>
+    <workbookView xWindow="440" yWindow="500" windowWidth="51200" windowHeight="28300" xr2:uid="{C1244F33-F08D-274A-A656-7DB80AA6BA4E}"/>
   </bookViews>
   <sheets>
     <sheet name="publications" sheetId="1" r:id="rId1"/>
@@ -906,7 +906,7 @@
     <t>type</t>
   </si>
   <si>
-    <t>Journal Articles</t>
+    <t>manuscripts</t>
   </si>
 </sst>
 </file>

--- a/markdown_generator/publications.xlsx
+++ b/markdown_generator/publications.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wchoi/Github-Repositories/wonchan-choi.github.io/markdown_generator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B3091AA-B165-664A-A897-1C8F2D842869}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1CE58AE-465D-6042-A2C3-35B2091B4934}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="440" yWindow="500" windowWidth="51200" windowHeight="28300" xr2:uid="{C1244F33-F08D-274A-A656-7DB80AA6BA4E}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="76">
   <si>
     <t>pub_date</t>
   </si>
@@ -1884,6 +1884,9 @@
       <c r="H2" s="1" t="s">
         <v>59</v>
       </c>
+      <c r="I2" s="1" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="3" spans="1:9" ht="51" x14ac:dyDescent="0.2">
       <c r="A3" s="3">
@@ -2229,6 +2232,7 @@
   <phoneticPr fontId="18" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1" xr:uid="{35C9EA02-369B-E84D-9225-C6DD2AC49F17}"/>
+    <hyperlink ref="I2" r:id="rId2" xr:uid="{91B869F6-9E64-9C49-B24F-9ADA03CC2DC6}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/markdown_generator/publications.xlsx
+++ b/markdown_generator/publications.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wchoi/Github-Repositories/wonchan-choi.github.io/markdown_generator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{342FFD24-1ED3-7247-BAF1-D85B4CD9DD13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AE74752-F10B-0740-AE72-03A11403962A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="49980" windowHeight="28300" xr2:uid="{C1244F33-F08D-274A-A656-7DB80AA6BA4E}"/>
   </bookViews>
@@ -161,12 +161,6 @@
     <t>Annual Meeting of the Association for Information Science &amp; Technology</t>
   </si>
   <si>
-    <t xml:space="preserve">Zheng, Z., Oh, H., Mim, M., Choi, W., &amp; Lee, Y. (2023). An exploration of robot-mediated Tai Chi exercise for older adults. Applied Sciences, 13(9), 5306. https://doi.org/10.3390/app13095306 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Choi, W., Stvilia, B. &amp; Lee, H. S. (2023). Developing a platform-specific framework for web credibility assessment: A case of social Q&amp;A sites. Information Processing and Management, 60(3), 103321. https://doi.org/10.1016/j.ipm.2023.103321 </t>
-  </si>
-  <si>
     <t xml:space="preserve">Choi, W., Kim, S.Y., &amp; Luo, M. (2022). Design matters in web credibility assessment: Interactive design as a social validation tool for online health information seekers. Asian Communication Research, 19(3), 119–138. https://doi.org/10.20879/acr.2022.19.3.119 </t>
   </si>
   <si>
@@ -378,13 +372,96 @@
   </si>
   <si>
     <t>San Diego, CA</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Zheng, Z., Oh, H., Mim, M., </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Choi, W.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, &amp; Lee, Y. (2023). An exploration of robot-mediated Tai Chi exercise for older adults. </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Applied Sciences</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, 13(9), 5306. https://doi.org/10.3390/app13095306 </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Choi, W.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, Stvilia, B. &amp; Lee, H. S. (2023). Developing a platform-specific framework for web credibility assessment: A case of social Q&amp;A sites. </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Information Processing and Management</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, 60(3), 103321. https://doi.org/10.1016/j.ipm.2023.103321 </t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="23" x14ac:knownFonts="1">
+  <fonts count="25" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -552,6 +629,20 @@
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <i/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -895,7 +986,7 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="42" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -916,9 +1007,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1305,7 +1393,7 @@
     <col min="4" max="4" width="21.1640625" style="6" customWidth="1"/>
     <col min="5" max="5" width="21.1640625" style="7" customWidth="1"/>
     <col min="6" max="6" width="68.6640625" style="2" customWidth="1"/>
-    <col min="7" max="7" width="74.5" style="8"/>
+    <col min="7" max="7" width="74.5" style="2"/>
     <col min="8" max="8" width="27.33203125" style="2" customWidth="1"/>
     <col min="9" max="16384" width="74.5" style="2"/>
   </cols>
@@ -1324,12 +1412,12 @@
         <v>2</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="2" t="s">
         <v>4</v>
       </c>
       <c r="H1" s="2" t="s">
@@ -1360,7 +1448,7 @@
         <v>24</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>42</v>
+        <v>113</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>25</v>
@@ -1380,14 +1468,14 @@
         <v>39</v>
       </c>
       <c r="C3" s="2" t="str">
-        <f t="shared" ref="C3:D23" si="0">MID(G3, FIND(").", G3) + 3, FIND(".", G3, FIND(").", G3) + 2) - FIND(").", G3) - 3)</f>
+        <f t="shared" ref="C3:C23" si="0">MID(G3, FIND(").", G3) + 3, FIND(".", G3, FIND(").", G3) + 2) - FIND(").", G3) - 3)</f>
         <v>Developing a platform-specific framework for web credibility assessment: A case of social Q&amp;A sites</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>9</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>43</v>
+        <v>114</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>26</v>
@@ -1408,7 +1496,7 @@
         <v>10</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>27</v>
@@ -1429,7 +1517,7 @@
         <v>11</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>28</v>
@@ -1450,7 +1538,7 @@
         <v>12</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>29</v>
@@ -1471,7 +1559,7 @@
         <v>13</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>30</v>
@@ -1492,7 +1580,7 @@
         <v>14</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>31</v>
@@ -1513,7 +1601,7 @@
         <v>15</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>32</v>
@@ -1534,7 +1622,7 @@
         <v>16</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>30</v>
@@ -1555,7 +1643,7 @@
         <v>17</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>33</v>
@@ -1576,7 +1664,7 @@
         <v>18</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>34</v>
@@ -1597,7 +1685,7 @@
         <v>19</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>19</v>
@@ -1618,7 +1706,7 @@
         <v>20</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>35</v>
@@ -1639,7 +1727,7 @@
         <v>21</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>36</v>
@@ -1660,7 +1748,7 @@
         <v>17</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>33</v>
@@ -1681,7 +1769,7 @@
         <v>16</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>30</v>
@@ -1702,7 +1790,7 @@
         <v>22</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>37</v>
@@ -1723,7 +1811,7 @@
         <v>21</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>36</v>
@@ -1744,10 +1832,10 @@
         <v>41</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="H20"/>
     </row>
@@ -1766,10 +1854,10 @@
         <v>41</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="51" x14ac:dyDescent="0.2">
@@ -1784,13 +1872,13 @@
         <v>Developing a theoretical framework for web credibility assessment on social Q&amp;A sites: Prelinary findings</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="51" x14ac:dyDescent="0.2">
@@ -1805,13 +1893,13 @@
         <v>Toward developing a framework for web credibility assessment on social Q&amp;A sites</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="51" x14ac:dyDescent="0.2">
@@ -1822,16 +1910,16 @@
         <v>40</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="68" x14ac:dyDescent="0.2">
@@ -1842,16 +1930,16 @@
         <v>40</v>
       </c>
       <c r="C25" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D25" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="D25" s="6" t="s">
-        <v>102</v>
-      </c>
       <c r="E25" s="7" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="68" x14ac:dyDescent="0.2">
@@ -1866,13 +1954,13 @@
         <v>When design matters in credibility assessment of health-related websites</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="68" x14ac:dyDescent="0.2">
@@ -1890,10 +1978,10 @@
         <v>41</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="68" x14ac:dyDescent="0.2">
@@ -1911,10 +1999,10 @@
         <v>41</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="68" x14ac:dyDescent="0.2">
@@ -1932,10 +2020,10 @@
         <v>41</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="68" x14ac:dyDescent="0.2">
@@ -1953,10 +2041,10 @@
         <v>41</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="68" x14ac:dyDescent="0.2">
@@ -1974,10 +2062,10 @@
         <v>41</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="68" x14ac:dyDescent="0.2">
@@ -1995,10 +2083,10 @@
         <v>41</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="68" x14ac:dyDescent="0.2">
@@ -2016,10 +2104,10 @@
         <v>41</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="68" x14ac:dyDescent="0.2">
@@ -2037,10 +2125,10 @@
         <v>41</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="68" x14ac:dyDescent="0.2">
@@ -2058,10 +2146,10 @@
         <v>41</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="68" x14ac:dyDescent="0.2">
@@ -2079,10 +2167,10 @@
         <v>41</v>
       </c>
       <c r="E36" s="7" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="68" x14ac:dyDescent="0.2">
@@ -2100,10 +2188,10 @@
         <v>41</v>
       </c>
       <c r="E37" s="7" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="G37" s="5" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="68" x14ac:dyDescent="0.2">
@@ -2121,10 +2209,10 @@
         <v>41</v>
       </c>
       <c r="E38" s="7" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="68" x14ac:dyDescent="0.2">
@@ -2142,10 +2230,10 @@
         <v>41</v>
       </c>
       <c r="E39" s="7" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="68" x14ac:dyDescent="0.2">
@@ -2163,10 +2251,10 @@
         <v>41</v>
       </c>
       <c r="E40" s="7" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G40" s="5" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="68" x14ac:dyDescent="0.2">
@@ -2184,10 +2272,10 @@
         <v>41</v>
       </c>
       <c r="E41" s="7" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G41" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="42" spans="1:7" ht="68" x14ac:dyDescent="0.2">
@@ -2205,10 +2293,10 @@
         <v>41</v>
       </c>
       <c r="E42" s="7" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G42" s="5" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="68" x14ac:dyDescent="0.2">
@@ -2226,10 +2314,10 @@
         <v>41</v>
       </c>
       <c r="E43" s="7" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G43" s="5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="44" spans="1:7" ht="68" x14ac:dyDescent="0.2">
@@ -2247,10 +2335,10 @@
         <v>41</v>
       </c>
       <c r="E44" s="7" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G44" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="68" x14ac:dyDescent="0.2">
@@ -2268,10 +2356,10 @@
         <v>41</v>
       </c>
       <c r="E45" s="7" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G45" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="46" spans="1:7" ht="68" x14ac:dyDescent="0.2">
@@ -2289,10 +2377,10 @@
         <v>41</v>
       </c>
       <c r="E46" s="7" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G46" s="5" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="68" x14ac:dyDescent="0.2">
@@ -2310,10 +2398,10 @@
         <v>41</v>
       </c>
       <c r="E47" s="7" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G47" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="68" x14ac:dyDescent="0.2">
@@ -2331,10 +2419,10 @@
         <v>41</v>
       </c>
       <c r="E48" s="7" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G48" s="5" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="49" spans="1:7" ht="68" x14ac:dyDescent="0.2">
@@ -2352,10 +2440,10 @@
         <v>41</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G49" s="5" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="50" spans="1:7" ht="68" x14ac:dyDescent="0.2">
@@ -2373,10 +2461,10 @@
         <v>41</v>
       </c>
       <c r="E50" s="7" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G50" s="5" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="51" spans="1:7" ht="68" x14ac:dyDescent="0.2">
@@ -2394,10 +2482,10 @@
         <v>41</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G51" s="5" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="52" spans="1:7" ht="68" x14ac:dyDescent="0.2">
@@ -2415,10 +2503,10 @@
         <v>41</v>
       </c>
       <c r="E52" s="7" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G52" s="5" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="53" spans="1:7" ht="68" x14ac:dyDescent="0.2">
@@ -2436,10 +2524,10 @@
         <v>41</v>
       </c>
       <c r="E53" s="7" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G53" s="5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="54" spans="1:7" ht="68" x14ac:dyDescent="0.2">
@@ -2457,10 +2545,10 @@
         <v>41</v>
       </c>
       <c r="E54" s="7" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G54" s="5" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
   </sheetData>

--- a/markdown_generator/publications.xlsx
+++ b/markdown_generator/publications.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wchoi/Github-Repositories/wonchan-choi.github.io/markdown_generator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AE74752-F10B-0740-AE72-03A11403962A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{424E90FD-3797-384F-9152-034BB8ACCC4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="49980" windowHeight="28300" xr2:uid="{C1244F33-F08D-274A-A656-7DB80AA6BA4E}"/>
+    <workbookView xWindow="-50260" yWindow="500" windowWidth="49880" windowHeight="28300" xr2:uid="{C1244F33-F08D-274A-A656-7DB80AA6BA4E}"/>
   </bookViews>
   <sheets>
     <sheet name="publications" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="121">
   <si>
     <t>pub_date</t>
   </si>
@@ -456,12 +456,72 @@
       <t xml:space="preserve">, 60(3), 103321. https://doi.org/10.1016/j.ipm.2023.103321 </t>
     </r>
   </si>
+  <si>
+    <t>Help-seeking situations related to visual interactions on mobile platforms and recommended designs for blind and visually impaired users</t>
+  </si>
+  <si>
+    <t>Journal of Imaging</t>
+  </si>
+  <si>
+    <t>While it is common for blind and visually impaired (BVI) users to use mobile devices to search for information, little research has explored the accessibility issues they encounter in their interactions with information retrieval systems, in particular digital libraries (DLs). This study represents one of the most comprehensive research projects, investigating accessibility issues, especially help-seeking situations BVI users face in their DL search processes. One hundred and twenty BVI users were recruited to search for information in six DLs on four types of mobile devices (iPhone, iPad, Android phone, and Android tablet), and multiple data collection methods were employed: questionnaires, think-aloud protocols, transaction logs, and interviews. This paper reports part of a large-scale study, including the categories of help-seeking situations BVI users face in their interactions with DLs, focusing on seven types of help-seeking situations related to visual interactions on mobile platforms: difficulty finding a toggle-based search feature, difficulty understanding a video feature, difficulty navigating items on paginated sections, difficulty distinguishing collection labels from thumbnails, difficulty recognizing the content of images, difficulty recognizing the content of graphs, and difficulty interacting with multilayered windows. Moreover, corresponding design recommendations are also proposed: placing meaningful labels for icon-based features in an easy-to-access location, offering intuitive and informative video descriptions for video players, providing structure information about a paginated section, separating collection/item titles from thumbnail descriptions, incorporating artificial intelligence image/graph recognition mechanisms, and limiting screen reader interactions to active windows. Additionally, the limitations of the study and future research are discussed.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Xie, I., </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Choi, W.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, Wang, S., Lee, H. S., Hong, B. H., Wang, N.-C., &amp; Cudjoe, E. K. (2024). Help-seeking situations related to visual interactions on mobile platforms and recommended designs for blind and visually impaired users. </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Journal of Imaging, 10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(8), 205. https://doi.org/10.3390/jimaging10080205</t>
+    </r>
+  </si>
+  <si>
+    <t>JI</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.3390/jimaging10080205</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="25" x14ac:knownFonts="1">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -643,6 +703,13 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -986,7 +1053,7 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="42" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1007,6 +1074,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1385,17 +1455,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AA85793-BCD8-2741-A85B-C8AEED21BC9A}">
-  <dimension ref="A1:J54"/>
+  <dimension ref="A1:J55"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="74.5" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" width="20.33203125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="74.5" style="2"/>
-    <col min="4" max="4" width="21.1640625" style="6" customWidth="1"/>
-    <col min="5" max="5" width="21.1640625" style="7" customWidth="1"/>
+    <col min="1" max="1" width="8.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.1640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="74" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.33203125" style="6" customWidth="1"/>
+    <col min="5" max="5" width="18" style="7" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="68.6640625" style="2" customWidth="1"/>
     <col min="7" max="7" width="74.5" style="2"/>
-    <col min="8" max="8" width="27.33203125" style="2" customWidth="1"/>
-    <col min="9" max="16384" width="74.5" style="2"/>
+    <col min="8" max="8" width="7.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="38.83203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="74.5" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="17" x14ac:dyDescent="0.2">
@@ -1430,570 +1502,575 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="289" x14ac:dyDescent="0.2">
-      <c r="A2" s="3">
+    <row r="2" spans="1:10" ht="404" x14ac:dyDescent="0.2">
+      <c r="A2" s="8">
+        <v>45526</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="289" x14ac:dyDescent="0.2">
+      <c r="A3" s="3">
         <v>45287</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="C2" s="2" t="str">
-        <f>MID(G2, FIND(").", G2) + 3, FIND(".", G2, FIND(").", G2) + 2) - FIND(").", G2) - 3)</f>
-        <v>An exploration of robot-mediated Tai Chi exercise for older adults</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="51" x14ac:dyDescent="0.2">
-      <c r="A3" s="3">
-        <v>45288</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C3" s="2" t="str">
-        <f t="shared" ref="C3:C23" si="0">MID(G3, FIND(").", G3) + 3, FIND(".", G3, FIND(").", G3) + 2) - FIND(").", G3) - 3)</f>
-        <v>Developing a platform-specific framework for web credibility assessment: A case of social Q&amp;A sites</v>
+        <f>MID(G3, FIND(").", G3) + 3, FIND(".", G3, FIND(").", G3) + 2) - FIND(").", G3) - 3)</f>
+        <v>An exploration of robot-mediated Tai Chi exercise for older adults</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A4" s="3">
-        <v>44924</v>
+        <v>45288</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C4" s="2" t="str">
+        <f t="shared" ref="C4:C24" si="0">MID(G4, FIND(").", G4) + 3, FIND(".", G4, FIND(").", G4) + 2) - FIND(").", G4) - 3)</f>
+        <v>Developing a platform-specific framework for web credibility assessment: A case of social Q&amp;A sites</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="A5" s="3">
+        <v>44924</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Design matters in web credibility assessment: Interactive design as a social validation tool for online health information seekers</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D5" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G5" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="H5" s="2" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="68" x14ac:dyDescent="0.2">
-      <c r="A5" s="3">
+    <row r="6" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="A6" s="3">
         <v>44925</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B6" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C5" s="2" t="str">
+      <c r="C6" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Understanding the research landscape of information and communication technology integration in dementia-focused assistive technologies: Mining literature from 1970 to 2020</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D6" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G6" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="H6" s="2" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="68" x14ac:dyDescent="0.2">
-      <c r="A6" s="3">
+    <row r="7" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="A7" s="3">
         <v>44926</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B7" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C6" s="2" t="str">
+      <c r="C7" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Respite service use among dementia and nondementia caregivers: Findings from the National Caregiving in the U</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D7" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G7" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="H6" s="2" t="s">
+      <c r="H7" s="2" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="85" x14ac:dyDescent="0.2">
-      <c r="A7" s="3">
+    <row r="8" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+      <c r="A8" s="3">
         <v>44562</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B8" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C7" s="2" t="str">
+      <c r="C8" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Associations between mastery of life and everyday life information-seeking behavior among older adults: Analysis of the Pew Research Center’s information engaged and information wary survey data</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D8" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="G8" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="H7" s="2" t="s">
+      <c r="H8" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="68" x14ac:dyDescent="0.2">
-      <c r="A8" s="3">
+    <row r="9" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="A9" s="3">
         <v>44198</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B9" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C8" s="2" t="str">
+      <c r="C9" s="2" t="str">
         <f t="shared" si="0"/>
         <v>A feature-oriented analysis of developers’ descriptions and user reviews of top mHealth applications for diabetes and hypertension</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D9" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="G9" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="H8" s="2" t="s">
+      <c r="H9" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="68" x14ac:dyDescent="0.2">
-      <c r="A9" s="3">
+    <row r="10" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="A10" s="3">
         <v>43833</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B10" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C9" s="2" t="str">
+      <c r="C10" s="2" t="str">
         <f t="shared" si="0"/>
         <v>A systematic review of mobile health technologies to support self-management of concurrent diabetes and hypertension</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D10" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="G9" s="4" t="s">
+      <c r="G10" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="H9" s="2" t="s">
+      <c r="H10" s="2" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="68" x14ac:dyDescent="0.2">
-      <c r="A10" s="3">
+    <row r="11" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="A11" s="3">
         <v>43469</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B11" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C10" s="2" t="str">
+      <c r="C11" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Older adults’ credibility assessment of online health information: An exploratory study using an extended typology of web credibility</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D11" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="G10" s="4" t="s">
+      <c r="G11" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="H10" s="2" t="s">
+      <c r="H11" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="51" x14ac:dyDescent="0.2">
-      <c r="A11" s="3">
+    <row r="12" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="A12" s="3">
         <v>43470</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B12" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C11" s="2" t="str">
+      <c r="C12" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Older adults’ health information behavior in everyday life settings</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D12" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="G11" s="4" t="s">
+      <c r="G12" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="H11" s="2" t="s">
+      <c r="H12" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="51" x14ac:dyDescent="0.2">
-      <c r="A12" s="3">
+    <row r="13" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="A13" s="3">
         <v>43471</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B13" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C12" s="2" t="str">
+      <c r="C13" s="2" t="str">
         <f t="shared" si="0"/>
         <v>mHealth technologies for osteoarthritis self-management and treatment: A systematic review</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="D13" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="G12" s="4" t="s">
+      <c r="G13" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="H12" s="2" t="s">
+      <c r="H13" s="2" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="51" x14ac:dyDescent="0.2">
-      <c r="A13" s="3">
+    <row r="14" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="A14" s="3">
         <v>42742</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B14" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C13" s="2" t="str">
+      <c r="C14" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Using mHealth app to support treatment decision making for knee arthritis: Patient perspective</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="D14" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="G13" s="4" t="s">
+      <c r="G14" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="H13" s="2" t="s">
+      <c r="H14" s="2" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="51" x14ac:dyDescent="0.2">
-      <c r="A14" s="3">
+    <row r="15" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="A15" s="3">
         <v>42012</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B15" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C14" s="2" t="str">
+      <c r="C15" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Publication and citation patterns of Korean LIS research by subject areas</v>
       </c>
-      <c r="D14" s="6" t="s">
+      <c r="D15" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="4" t="s">
+      <c r="G15" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="H14" s="2" t="s">
+      <c r="H15" s="2" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="68" x14ac:dyDescent="0.2">
-      <c r="A15" s="3">
+    <row r="16" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="A16" s="3">
         <v>42013</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B16" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C15" s="2" t="str">
+      <c r="C16" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Looking beyond the numbers: Bibliometric approach to analysis of LIS research in Korea</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="D16" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="G15" s="4" t="s">
+      <c r="G16" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="H15" s="2" t="s">
+      <c r="H16" s="2" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="51" x14ac:dyDescent="0.2">
-      <c r="A16" s="3">
+    <row r="17" spans="1:8" ht="51" x14ac:dyDescent="0.2">
+      <c r="A17" s="3">
         <v>42014</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B17" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C16" s="2" t="str">
+      <c r="C17" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Mobile wellness application-seeking behavior by college students: An exploratory study</v>
       </c>
-      <c r="D16" s="6" t="s">
+      <c r="D17" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="G16" s="4" t="s">
+      <c r="G17" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="H16" s="2" t="s">
+      <c r="H17" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="68" x14ac:dyDescent="0.2">
-      <c r="A17" s="3">
+    <row r="18" spans="1:8" ht="68" x14ac:dyDescent="0.2">
+      <c r="A18" s="3">
         <v>42015</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B18" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C17" s="2" t="str">
+      <c r="C18" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Web credibility assessment: Conceptualization, operationalization, variability, and models</v>
       </c>
-      <c r="D17" s="6" t="s">
+      <c r="D18" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="G17" s="4" t="s">
+      <c r="G18" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="H17" s="2" t="s">
+      <c r="H18" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="51" x14ac:dyDescent="0.2">
-      <c r="A18" s="3">
+    <row r="19" spans="1:8" ht="51" x14ac:dyDescent="0.2">
+      <c r="A19" s="3">
         <v>39459</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B19" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C18" s="2" t="str">
+      <c r="C19" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Developing and testing of an e-journal evaluation model for university libraries</v>
       </c>
-      <c r="D18" s="6" t="s">
+      <c r="D19" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="G18" s="4" t="s">
+      <c r="G19" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="H18" s="2" t="s">
+      <c r="H19" s="2" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="51" x14ac:dyDescent="0.2">
-      <c r="A19" s="3">
+    <row r="20" spans="1:8" ht="51" x14ac:dyDescent="0.2">
+      <c r="A20" s="3">
         <v>39460</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B20" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C19" s="2" t="str">
+      <c r="C20" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Trends in integrated electronic resource management in academic libraries</v>
       </c>
-      <c r="D19" s="6" t="s">
+      <c r="D20" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="G19" s="4" t="s">
+      <c r="G20" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="H19" s="2" t="s">
+      <c r="H20" s="2" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="68" x14ac:dyDescent="0.2">
-      <c r="A20" s="3">
+    <row r="21" spans="1:8" ht="68" x14ac:dyDescent="0.2">
+      <c r="A21" s="3">
         <v>39461</v>
       </c>
-      <c r="B20" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C20" s="2" t="str">
+      <c r="B21" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C21" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Preliminary findings on developing a scale for credibility assessment on interactive web platforms</v>
       </c>
-      <c r="D20" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="E20" s="7" t="s">
+      <c r="D21" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="E21" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="G20" s="5" t="s">
+      <c r="G21" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="H20"/>
-    </row>
-    <row r="21" spans="1:8" ht="68" x14ac:dyDescent="0.2">
-      <c r="A21" s="3">
+      <c r="H21"/>
+    </row>
+    <row r="22" spans="1:8" ht="68" x14ac:dyDescent="0.2">
+      <c r="A22" s="3">
         <v>39462</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C21" s="2" t="str">
+      <c r="B22" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C22" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Exploring applications and user experience with generative AI tools: A content analysis of reddit posts on ChatGPT</v>
       </c>
-      <c r="D21" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="E21" s="7" t="s">
+      <c r="D22" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="E22" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="G21" s="5" t="s">
+      <c r="G22" s="5" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="51" x14ac:dyDescent="0.2">
-      <c r="A22" s="3">
+    <row r="23" spans="1:8" ht="51" x14ac:dyDescent="0.2">
+      <c r="A23" s="3">
         <v>39463</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C22" s="2" t="str">
+      <c r="B23" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C23" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Developing a theoretical framework for web credibility assessment on social Q&amp;A sites: Prelinary findings</v>
       </c>
-      <c r="D22" s="6" t="s">
+      <c r="D23" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="E22" s="7" t="s">
+      <c r="E23" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="G22" s="5" t="s">
+      <c r="G23" s="5" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="51" x14ac:dyDescent="0.2">
-      <c r="A23" s="3">
+    <row r="24" spans="1:8" ht="51" x14ac:dyDescent="0.2">
+      <c r="A24" s="3">
         <v>39464</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C23" s="2" t="str">
+      <c r="B24" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C24" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Toward developing a framework for web credibility assessment on social Q&amp;A sites</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="D24" s="6" t="s">
         <v>99</v>
-      </c>
-      <c r="E23" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="G23" s="5" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" ht="51" x14ac:dyDescent="0.2">
-      <c r="A24" s="3">
-        <v>39465</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="D24" s="6" t="s">
-        <v>95</v>
       </c>
       <c r="E24" s="7" t="s">
         <v>96</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" ht="68" x14ac:dyDescent="0.2">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="51" x14ac:dyDescent="0.2">
       <c r="A25" s="3">
-        <v>39466</v>
+        <v>39465</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>40</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E25" s="7" t="s">
         <v>96</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="68" x14ac:dyDescent="0.2">
       <c r="A26" s="3">
-        <v>39467</v>
+        <v>39466</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C26" s="2" t="str">
-        <f t="shared" ref="C26:C54" si="1">MID(G26, FIND(").", G26) + 3, FIND(".", G26, FIND(").", G26) + 2) - FIND(").", G26) - 3)</f>
-        <v>When design matters in credibility assessment of health-related websites</v>
+      <c r="C26" s="2" t="s">
+        <v>98</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E26" s="7" t="s">
         <v>96</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="68" x14ac:dyDescent="0.2">
       <c r="A27" s="3">
-        <v>39468</v>
+        <v>39467</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>40</v>
       </c>
       <c r="C27" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>Can a robot encourage physical exercise for older adults? A pilot robot-mediated Tai Chi exercise study</v>
+        <f t="shared" ref="C27:C55" si="1">MID(G27, FIND(").", G27) + 3, FIND(".", G27, FIND(").", G27) + 2) - FIND(").", G27) - 3)</f>
+        <v>When design matters in credibility assessment of health-related websites</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>41</v>
+        <v>101</v>
       </c>
       <c r="E27" s="7" t="s">
         <v>96</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="68" x14ac:dyDescent="0.2">
       <c r="A28" s="3">
-        <v>39469</v>
+        <v>39468</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>40</v>
       </c>
       <c r="C28" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>Validating an extended typology of web credibility assessment</v>
+        <v>Can a robot encourage physical exercise for older adults? A pilot robot-mediated Tai Chi exercise study</v>
       </c>
       <c r="D28" s="6" t="s">
         <v>41</v>
@@ -2002,61 +2079,61 @@
         <v>96</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="68" x14ac:dyDescent="0.2">
       <c r="A29" s="3">
-        <v>39470</v>
+        <v>39469</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>40</v>
       </c>
       <c r="C29" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>Challenges in self-management among older adults with hypertension and diabetes</v>
+        <v>Validating an extended typology of web credibility assessment</v>
       </c>
       <c r="D29" s="6" t="s">
         <v>41</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="68" x14ac:dyDescent="0.2">
       <c r="A30" s="3">
-        <v>39471</v>
+        <v>39470</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>40</v>
       </c>
       <c r="C30" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>Analyzing divergent methodologies for political fact checking: United States and South Korea</v>
+        <v>Challenges in self-management among older adults with hypertension and diabetes</v>
       </c>
       <c r="D30" s="6" t="s">
         <v>41</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="68" x14ac:dyDescent="0.2">
       <c r="A31" s="3">
-        <v>39472</v>
+        <v>39471</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>40</v>
       </c>
       <c r="C31" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>Assessing the informativeness of user reviews on mobile health applications for chronic diseases</v>
+        <v>Analyzing divergent methodologies for political fact checking: United States and South Korea</v>
       </c>
       <c r="D31" s="6" t="s">
         <v>41</v>
@@ -2065,208 +2142,208 @@
         <v>103</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="68" x14ac:dyDescent="0.2">
       <c r="A32" s="3">
-        <v>39473</v>
+        <v>39472</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>40</v>
       </c>
       <c r="C32" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>Assistive technologies for older adults with MCC to support self-management</v>
+        <v>Assessing the informativeness of user reviews on mobile health applications for chronic diseases</v>
       </c>
       <c r="D32" s="6" t="s">
         <v>41</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="68" x14ac:dyDescent="0.2">
       <c r="A33" s="3">
-        <v>39474</v>
+        <v>39473</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>40</v>
       </c>
       <c r="C33" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>Effects of user interface design and task complexity level on user experience in an mHealth application</v>
+        <v>Assistive technologies for older adults with MCC to support self-management</v>
       </c>
       <c r="D33" s="6" t="s">
         <v>41</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="68" x14ac:dyDescent="0.2">
       <c r="A34" s="3">
-        <v>39475</v>
+        <v>39474</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>40</v>
       </c>
       <c r="C34" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>Validating a single-item stress scale for mHealth interventions</v>
+        <v>Effects of user interface design and task complexity level on user experience in an mHealth application</v>
       </c>
       <c r="D34" s="6" t="s">
         <v>41</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="68" x14ac:dyDescent="0.2">
       <c r="A35" s="3">
-        <v>39476</v>
+        <v>39475</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>40</v>
       </c>
       <c r="C35" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>Effective use of user interface and user experience in an mHealth application</v>
+        <v>Validating a single-item stress scale for mHealth interventions</v>
       </c>
       <c r="D35" s="6" t="s">
         <v>41</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="68" x14ac:dyDescent="0.2">
       <c r="A36" s="3">
-        <v>39477</v>
+        <v>39476</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>40</v>
       </c>
       <c r="C36" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>A framework to design mHealth apps for supporting self-management of chronic disease</v>
+        <v>Effective use of user interface and user experience in an mHealth application</v>
       </c>
       <c r="D36" s="6" t="s">
         <v>41</v>
       </c>
       <c r="E36" s="7" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="68" x14ac:dyDescent="0.2">
       <c r="A37" s="3">
-        <v>39478</v>
+        <v>39477</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>40</v>
       </c>
       <c r="C37" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>Older adults’ health information behavior in the context of everyday life information seeking (ELIS)</v>
+        <v>A framework to design mHealth apps for supporting self-management of chronic disease</v>
       </c>
       <c r="D37" s="6" t="s">
         <v>41</v>
       </c>
       <c r="E37" s="7" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G37" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="68" x14ac:dyDescent="0.2">
       <c r="A38" s="3">
-        <v>39479</v>
+        <v>39478</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>40</v>
       </c>
       <c r="C38" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>TJR App: A mobile app for shared informed decision making in total joint replacement surgery</v>
+        <v>Older adults’ health information behavior in the context of everyday life information seeking (ELIS)</v>
       </c>
       <c r="D38" s="6" t="s">
         <v>41</v>
       </c>
       <c r="E38" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="68" x14ac:dyDescent="0.2">
       <c r="A39" s="3">
-        <v>39480</v>
+        <v>39479</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>40</v>
       </c>
       <c r="C39" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>Using mHealth app to support TKR decision making for knee arthritis patients</v>
+        <v>TJR App: A mobile app for shared informed decision making in total joint replacement surgery</v>
       </c>
       <c r="D39" s="6" t="s">
         <v>41</v>
       </c>
       <c r="E39" s="7" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="68" x14ac:dyDescent="0.2">
       <c r="A40" s="3">
-        <v>39481</v>
+        <v>39480</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>40</v>
       </c>
       <c r="C40" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>Developing an mHealth application for osteoarthritis patients</v>
+        <v>Using mHealth app to support TKR decision making for knee arthritis patients</v>
       </c>
       <c r="D40" s="6" t="s">
         <v>41</v>
       </c>
       <c r="E40" s="7" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G40" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="68" x14ac:dyDescent="0.2">
       <c r="A41" s="3">
-        <v>39482</v>
+        <v>39481</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>40</v>
       </c>
       <c r="C41" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>A single-item stress scale for mHealth interventions</v>
+        <v>Developing an mHealth application for osteoarthritis patients</v>
       </c>
       <c r="D41" s="6" t="s">
         <v>41</v>
@@ -2275,19 +2352,19 @@
         <v>112</v>
       </c>
       <c r="G41" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="42" spans="1:7" ht="68" x14ac:dyDescent="0.2">
       <c r="A42" s="3">
-        <v>39483</v>
+        <v>39482</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>40</v>
       </c>
       <c r="C42" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>A new framework for web credibility assessment</v>
+        <v>A single-item stress scale for mHealth interventions</v>
       </c>
       <c r="D42" s="6" t="s">
         <v>41</v>
@@ -2296,19 +2373,19 @@
         <v>112</v>
       </c>
       <c r="G42" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="68" x14ac:dyDescent="0.2">
       <c r="A43" s="3">
-        <v>39484</v>
+        <v>39483</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>40</v>
       </c>
       <c r="C43" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>Older adults’ credibility assessment of online health information</v>
+        <v>A new framework for web credibility assessment</v>
       </c>
       <c r="D43" s="6" t="s">
         <v>41</v>
@@ -2317,19 +2394,19 @@
         <v>112</v>
       </c>
       <c r="G43" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="44" spans="1:7" ht="68" x14ac:dyDescent="0.2">
       <c r="A44" s="3">
-        <v>39485</v>
+        <v>39484</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>40</v>
       </c>
       <c r="C44" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>Implications of assessing the credibility of online Information for the LIS curriculum</v>
+        <v>Older adults’ credibility assessment of online health information</v>
       </c>
       <c r="D44" s="6" t="s">
         <v>41</v>
@@ -2338,19 +2415,19 @@
         <v>112</v>
       </c>
       <c r="G44" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="68" x14ac:dyDescent="0.2">
       <c r="A45" s="3">
-        <v>39486</v>
+        <v>39485</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>40</v>
       </c>
       <c r="C45" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>How do college students choose mobile health/wellness applications? 77th Annual Meeting of Association for Information Science &amp; Technology, Seattle, WA</v>
+        <v>Implications of assessing the credibility of online Information for the LIS curriculum</v>
       </c>
       <c r="D45" s="6" t="s">
         <v>41</v>
@@ -2359,19 +2436,19 @@
         <v>112</v>
       </c>
       <c r="G45" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="46" spans="1:7" ht="68" x14ac:dyDescent="0.2">
       <c r="A46" s="3">
-        <v>39487</v>
+        <v>39486</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>40</v>
       </c>
       <c r="C46" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>College students’ value structure of choosing and using mobile health/wellness applications: Preliminary findings</v>
+        <v>How do college students choose mobile health/wellness applications? 77th Annual Meeting of Association for Information Science &amp; Technology, Seattle, WA</v>
       </c>
       <c r="D46" s="6" t="s">
         <v>41</v>
@@ -2380,19 +2457,19 @@
         <v>112</v>
       </c>
       <c r="G46" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="68" x14ac:dyDescent="0.2">
       <c r="A47" s="3">
-        <v>39488</v>
+        <v>39487</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>40</v>
       </c>
       <c r="C47" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>Use of mobile wellness applications and perception of quality</v>
+        <v>College students’ value structure of choosing and using mobile health/wellness applications: Preliminary findings</v>
       </c>
       <c r="D47" s="6" t="s">
         <v>41</v>
@@ -2401,19 +2478,19 @@
         <v>112</v>
       </c>
       <c r="G47" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="68" x14ac:dyDescent="0.2">
       <c r="A48" s="3">
-        <v>39489</v>
+        <v>39488</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>40</v>
       </c>
       <c r="C48" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>Guidelines for older-adult-friendly online tutorial for Facebook: Content, design, and training principles</v>
+        <v>Use of mobile wellness applications and perception of quality</v>
       </c>
       <c r="D48" s="6" t="s">
         <v>41</v>
@@ -2422,19 +2499,19 @@
         <v>112</v>
       </c>
       <c r="G48" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="49" spans="1:7" ht="68" x14ac:dyDescent="0.2">
       <c r="A49" s="3">
-        <v>39490</v>
+        <v>39489</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>40</v>
       </c>
       <c r="C49" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>The Sonzogno digital library project</v>
+        <v>Guidelines for older-adult-friendly online tutorial for Facebook: Content, design, and training principles</v>
       </c>
       <c r="D49" s="6" t="s">
         <v>41</v>
@@ -2443,19 +2520,19 @@
         <v>112</v>
       </c>
       <c r="G49" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="50" spans="1:7" ht="68" x14ac:dyDescent="0.2">
       <c r="A50" s="3">
-        <v>39491</v>
+        <v>39490</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>40</v>
       </c>
       <c r="C50" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>Difference in citation rates by subject areas of LIS in Korea</v>
+        <v>The Sonzogno digital library project</v>
       </c>
       <c r="D50" s="6" t="s">
         <v>41</v>
@@ -2464,19 +2541,19 @@
         <v>112</v>
       </c>
       <c r="G50" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="51" spans="1:7" ht="68" x14ac:dyDescent="0.2">
       <c r="A51" s="3">
-        <v>39492</v>
+        <v>39491</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>40</v>
       </c>
       <c r="C51" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>Credibility assessment of online resources and perceived quality of mobile applications</v>
+        <v>Difference in citation rates by subject areas of LIS in Korea</v>
       </c>
       <c r="D51" s="6" t="s">
         <v>41</v>
@@ -2485,19 +2562,19 @@
         <v>112</v>
       </c>
       <c r="G51" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="52" spans="1:7" ht="68" x14ac:dyDescent="0.2">
       <c r="A52" s="3">
-        <v>39493</v>
+        <v>39492</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>40</v>
       </c>
       <c r="C52" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>What makes online health information credible for older adults?: An exploratory study</v>
+        <v>Credibility assessment of online resources and perceived quality of mobile applications</v>
       </c>
       <c r="D52" s="6" t="s">
         <v>41</v>
@@ -2506,19 +2583,19 @@
         <v>112</v>
       </c>
       <c r="G52" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="53" spans="1:7" ht="68" x14ac:dyDescent="0.2">
       <c r="A53" s="3">
-        <v>39494</v>
+        <v>39493</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>40</v>
       </c>
       <c r="C53" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>The impact of the public library on early reading achievement: Using the early childhood longitudinal study (ECLS) 1st grade student sample</v>
+        <v>What makes online health information credible for older adults?: An exploratory study</v>
       </c>
       <c r="D53" s="6" t="s">
         <v>41</v>
@@ -2527,19 +2604,19 @@
         <v>112</v>
       </c>
       <c r="G53" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="54" spans="1:7" ht="68" x14ac:dyDescent="0.2">
       <c r="A54" s="3">
-        <v>39495</v>
+        <v>39494</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>40</v>
       </c>
       <c r="C54" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>Senior citizens’ credibility assessment of online health information: A proposal of a mixed methods study</v>
+        <v>The impact of the public library on early reading achievement: Using the early childhood longitudinal study (ECLS) 1st grade student sample</v>
       </c>
       <c r="D54" s="6" t="s">
         <v>41</v>
@@ -2548,14 +2625,36 @@
         <v>112</v>
       </c>
       <c r="G54" s="5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" ht="68" x14ac:dyDescent="0.2">
+      <c r="A55" s="3">
+        <v>39495</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C55" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>Senior citizens’ credibility assessment of online health information: A proposal of a mixed methods study</v>
+      </c>
+      <c r="D55" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="E55" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="G55" s="5" t="s">
         <v>92</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="I2" r:id="rId1" xr:uid="{35C9EA02-369B-E84D-9225-C6DD2AC49F17}"/>
-    <hyperlink ref="J2" r:id="rId2" xr:uid="{91B869F6-9E64-9C49-B24F-9ADA03CC2DC6}"/>
+    <hyperlink ref="I3" r:id="rId1" xr:uid="{35C9EA02-369B-E84D-9225-C6DD2AC49F17}"/>
+    <hyperlink ref="J3" r:id="rId2" xr:uid="{91B869F6-9E64-9C49-B24F-9ADA03CC2DC6}"/>
+    <hyperlink ref="I2" r:id="rId3" xr:uid="{CF390CF6-A303-6740-B7C8-F24E9422F8DE}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
